--- a/교재/엑셀교재v2/008-009_가져오기와_붙여넣기_실습.xlsx
+++ b/교재/엑셀교재v2/008-009_가져오기와_붙여넣기_실습.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FORYOUCOM\Documents\CompUse2nd\교재\엑셀교재v2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\엑셀교재v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E6F903-5A80-4C3A-A1A4-347E1ABC1D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205398BB-7BEB-423B-A7B0-101749C6FDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36495" yWindow="3675" windowWidth="16380" windowHeight="11295" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25170" yWindow="450" windowWidth="22200" windowHeight="14790" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="가져오기_실습" sheetId="1" r:id="rId1"/>
@@ -26,11 +26,24 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">연결붙여넣기_정답!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>가져오기_실습</t>
   </si>
@@ -38,9 +51,6 @@
     <t>성취도.txt를 공백으로 구분하여 A3에 가져오세요. 표로 불러온 뒤 범위로 변환하세요. 결과는 A3:E11입니다.</t>
   </si>
   <si>
-    <t>사진 008페이지 기반 재구성 데이터입니다. 흐린 이름과 일부 학번은 실습용으로 보충했습니다. 정답 시트는 값과 위치 확인용 일반 범위입니다.</t>
-  </si>
-  <si>
     <t>가져오기_정답</t>
   </si>
   <si>
@@ -104,9 +114,6 @@
     <t>사장</t>
   </si>
   <si>
-    <t>정답 시트에는 실제 Excel에서 붙여넣은 그림이 들어 있습니다. 셀 값은 비어 있고, 클릭하면 그림 선택 테두리가 나타납니다.</t>
-  </si>
-  <si>
     <t>그림복사_정답</t>
   </si>
   <si>
@@ -132,9 +139,6 @@
   </si>
   <si>
     <t>인천</t>
-  </si>
-  <si>
-    <t>사진 009페이지의 지역 목록으로 만든 실습입니다. 정답 시트에서는 B3을 바꾸면 D3이 함께 바뀝니다.</t>
   </si>
   <si>
     <t>연결붙여넣기_정답</t>
@@ -156,11 +160,15 @@
     <font>
       <sz val="11"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
@@ -690,9 +698,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
@@ -875,7 +881,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -884,19 +890,19 @@
     </row>
     <row r="3" spans="1:14" ht="27" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -910,7 +916,7 @@
     </row>
     <row r="4" spans="1:14" ht="27" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5">
         <v>2510</v>
@@ -938,7 +944,7 @@
     </row>
     <row r="5" spans="1:14" ht="27" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5">
         <v>2611</v>
@@ -964,7 +970,7 @@
     </row>
     <row r="6" spans="1:14" ht="27" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5">
         <v>2612</v>
@@ -990,7 +996,7 @@
     </row>
     <row r="7" spans="1:14" ht="27" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5">
         <v>2313</v>
@@ -1016,7 +1022,7 @@
     </row>
     <row r="8" spans="1:14" ht="27" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5">
         <v>2314</v>
@@ -1042,7 +1048,7 @@
     </row>
     <row r="9" spans="1:14" ht="27" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5">
         <v>2415</v>
@@ -1068,7 +1074,7 @@
     </row>
     <row r="10" spans="1:14" ht="27" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5">
         <v>2616</v>
@@ -1086,9 +1092,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="9" t="s">
-        <v>2</v>
-      </c>
+      <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
@@ -1096,7 +1100,7 @@
     </row>
     <row r="11" spans="1:14" ht="27" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5">
         <v>2517</v>
@@ -1281,7 +1285,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -1315,7 +1319,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1375,19 +1379,19 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1422,9 +1426,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="9" t="s">
-        <v>24</v>
-      </c>
+      <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
@@ -1610,7 +1612,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -1644,7 +1646,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1709,9 +1711,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="9" t="s">
-        <v>24</v>
-      </c>
+      <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
@@ -1885,7 +1885,7 @@
     <row r="2" spans="1:14" ht="27" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1895,7 +1895,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -1905,7 +1905,7 @@
     <row r="3" spans="1:14" ht="27" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1923,7 +1923,7 @@
     <row r="4" spans="1:14" ht="27" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1933,7 +1933,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -1943,7 +1943,7 @@
     <row r="5" spans="1:14" ht="27" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1961,7 +1961,7 @@
     <row r="6" spans="1:14" ht="27" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1979,7 +1979,7 @@
     <row r="7" spans="1:14" ht="27" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -2036,9 +2036,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
@@ -2213,7 +2211,7 @@
     <row r="2" spans="1:14" ht="27" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="str">
@@ -2226,7 +2224,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
@@ -2236,7 +2234,7 @@
     <row r="3" spans="1:14" ht="27" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="str">
@@ -2257,7 +2255,7 @@
     <row r="4" spans="1:14" ht="27" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="str">
@@ -2270,7 +2268,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
@@ -2280,7 +2278,7 @@
     <row r="5" spans="1:14" ht="27" customHeight="1">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="str">
@@ -2301,7 +2299,7 @@
     <row r="6" spans="1:14" ht="27" customHeight="1">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="str">
@@ -2322,7 +2320,7 @@
     <row r="7" spans="1:14" ht="27" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="str">
@@ -2382,9 +2380,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="9" t="s">
-        <v>34</v>
-      </c>
+      <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
